--- a/jyx2/Assets/Mods/shendiao/Configs/武功.xlsx
+++ b/jyx2/Assets/Mods/shendiao/Configs/武功.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
@@ -322,13 +322,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -359,12 +359,12 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -760,7 +760,7 @@
         <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -786,7 +786,7 @@
         <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -812,7 +812,7 @@
         <v>28</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -838,7 +838,7 @@
         <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -864,7 +864,7 @@
         <v>34</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -890,7 +890,7 @@
         <v>37</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -916,7 +916,7 @@
         <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -942,7 +942,7 @@
         <v>43</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -968,7 +968,7 @@
         <v>46</v>
       </c>
       <c r="H13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -994,7 +994,7 @@
         <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1020,7 +1020,7 @@
         <v>52</v>
       </c>
       <c r="H15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1046,7 +1046,7 @@
         <v>55</v>
       </c>
       <c r="H16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1072,7 +1072,7 @@
         <v>58</v>
       </c>
       <c r="H17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1098,7 +1098,7 @@
         <v>61</v>
       </c>
       <c r="H18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1124,7 +1124,7 @@
         <v>64</v>
       </c>
       <c r="H19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1150,7 +1150,7 @@
         <v>67</v>
       </c>
       <c r="H20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1176,7 +1176,7 @@
         <v>70</v>
       </c>
       <c r="H21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1202,7 +1202,7 @@
         <v>73</v>
       </c>
       <c r="H22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1228,7 +1228,7 @@
         <v>76</v>
       </c>
       <c r="H23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1254,7 +1254,7 @@
         <v>40</v>
       </c>
       <c r="H24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1280,7 +1280,7 @@
         <v>73</v>
       </c>
       <c r="H25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1306,7 +1306,7 @@
         <v>73</v>
       </c>
       <c r="H26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1332,7 +1332,7 @@
         <v>85</v>
       </c>
       <c r="H27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1358,7 +1358,7 @@
         <v>88</v>
       </c>
       <c r="H28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1384,7 +1384,7 @@
         <v>91</v>
       </c>
       <c r="H29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1410,7 +1410,7 @@
         <v>40</v>
       </c>
       <c r="H30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1436,7 +1436,7 @@
         <v>40</v>
       </c>
       <c r="H31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1462,7 +1462,7 @@
         <v>40</v>
       </c>
       <c r="H32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1488,7 +1488,7 @@
         <v>40</v>
       </c>
       <c r="H33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
